--- a/ruoyi-fastapi-backend/数据库设计_4.15.xlsx
+++ b/ruoyi-fastapi-backend/数据库设计_4.15.xlsx
@@ -4,27 +4,27 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255" firstSheet="13" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="说明(README)" sheetId="1" r:id="rId1"/>
-    <sheet name="标准基础信息(Standard_Info)" sheetId="2" r:id="rId2"/>
-    <sheet name="标准引言表(Standard_Intro)" sheetId="3" r:id="rId3"/>
-    <sheet name="标准前言表(Standard_Preface)" sheetId="4" r:id="rId4"/>
-    <sheet name="提出单位(Proposing_Org)" sheetId="5" r:id="rId5"/>
-    <sheet name="归口单位(Responsible_Org)" sheetId="6" r:id="rId6"/>
-    <sheet name="起草人(Drafter)" sheetId="7" r:id="rId7"/>
-    <sheet name="起草单位(Drafting_Org)" sheetId="8" r:id="rId8"/>
-    <sheet name="标准正文内容(Standard_Content)" sheetId="9" r:id="rId9"/>
-    <sheet name="文档类型(Document_Type)" sheetId="10" r:id="rId10"/>
-    <sheet name="表内容(Table_Content)" sheetId="11" r:id="rId11"/>
-    <sheet name="表内容格式(Table_Content_Fmt)" sheetId="12" r:id="rId12"/>
-    <sheet name="图片(Image)" sheetId="13" r:id="rId13"/>
-    <sheet name="公式(Formula)" sheetId="14" r:id="rId14"/>
-    <sheet name="术语和定义(Terms_Defs)" sheetId="15" r:id="rId15"/>
-    <sheet name="术语和定义（引）(Terms_Ref)" sheetId="16" r:id="rId16"/>
-    <sheet name="规范性引用文件(Norm_Refs)" sheetId="17" r:id="rId17"/>
-    <sheet name="参考文献表(Bibliography)" sheetId="18" r:id="rId18"/>
+    <sheet name="标准基础信息Std_Standard_Info)" sheetId="2" r:id="rId2"/>
+    <sheet name="标准引言表(Std_Standard_Intro)" sheetId="3" r:id="rId3"/>
+    <sheet name="标准前言表(Std_Standard_Preface)" sheetId="4" r:id="rId4"/>
+    <sheet name="提出单位(Std_Proposing_Org)" sheetId="5" r:id="rId5"/>
+    <sheet name="归口单位(Std_Responsible_Org)" sheetId="6" r:id="rId6"/>
+    <sheet name="起草人(Std_Drafter)" sheetId="7" r:id="rId7"/>
+    <sheet name="起草单位(Std_Drafting_Org)" sheetId="8" r:id="rId8"/>
+    <sheet name="标准正文内容(Std_Standard_Content)" sheetId="9" r:id="rId9"/>
+    <sheet name="文档类型(Std_Document_Type)" sheetId="10" r:id="rId10"/>
+    <sheet name="表内容(Std_Table_Content)" sheetId="11" r:id="rId11"/>
+    <sheet name="表内容格式(Std_Table_Content_Fmt)" sheetId="12" r:id="rId12"/>
+    <sheet name="图片(Std_Image)" sheetId="13" r:id="rId13"/>
+    <sheet name="公式(Std_Formula)" sheetId="14" r:id="rId14"/>
+    <sheet name="术语和定义(Std_Terms_Defs)" sheetId="15" r:id="rId15"/>
+    <sheet name="术语和定义（引）(Std_Terms_Ref)" sheetId="16" r:id="rId16"/>
+    <sheet name="规范性引用文件(Std_Norm_Refs)" sheetId="17" r:id="rId17"/>
+    <sheet name="参考文献表(Std_Bibliography)" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
